--- a/data/trans_orig/P36B16-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B16-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,67 +760,67 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>13490</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>8988</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>21644</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>12859</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>7956</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>20162</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42719</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32704</t>
+          <t>32678</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55629</t>
+          <t>57390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>93633</t>
+          <t>94678</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80248</t>
+          <t>81980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112792</t>
+          <t>109245</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>136352</t>
+          <t>139214</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118821</t>
+          <t>122242</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159256</t>
+          <t>158027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>291241</t>
+          <t>325161</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269812</t>
+          <t>302061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>310287</t>
+          <t>348389</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>407448</t>
+          <t>439771</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>385385</t>
+          <t>416939</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>429186</t>
+          <t>461489</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>698689</t>
+          <t>764932</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>668525</t>
+          <t>732947</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>729387</t>
+          <t>799122</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>159814</t>
+          <t>185733</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>141333</t>
+          <t>164294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>181562</t>
+          <t>208969</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>230338</t>
+          <t>260428</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>213136</t>
+          <t>241300</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>250432</t>
+          <t>283810</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>390152</t>
+          <t>446161</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>360708</t>
+          <t>418879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>418894</t>
+          <t>476898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23372</t>
+          <t>26588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>18314</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>26274</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>35672</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22952</t>
+          <t>26051</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41899</t>
+          <t>47439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>754443</t>
+          <t>820939</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>754443</t>
+          <t>820939</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>754443</t>
+          <t>820939</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1269381</t>
+          <t>1399469</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1269381</t>
+          <t>1399469</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1269381</t>
+          <t>1399469</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25111</t>
+          <t>32462</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17386</t>
+          <t>21651</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>33378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>39871</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20982</t>
+          <t>28049</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>54813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>153916</t>
+          <t>167278</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105894</t>
+          <t>141743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>188583</t>
+          <t>200379</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>161661</t>
+          <t>182031</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116126</t>
+          <t>156981</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>194176</t>
+          <t>208033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>7,24%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>315577</t>
+          <t>349309</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250937</t>
+          <t>316340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>367680</t>
+          <t>391162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1223932</t>
+          <t>1307760</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>821427</t>
+          <t>1249326</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1385255</t>
+          <t>1362125</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1202024</t>
+          <t>1279346</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>902392</t>
+          <t>1237836</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1361091</t>
+          <t>1322043</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2425956</t>
+          <t>2587105</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1962600</t>
+          <t>2508334</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2685989</t>
+          <t>2649614</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>617995</t>
+          <t>691016</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>401018</t>
+          <t>640160</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>711201</t>
+          <t>742088</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>821077</t>
+          <t>641777</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>640637</t>
+          <t>600851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1198074</t>
+          <t>681928</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1439073</t>
+          <t>1332794</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1188861</t>
+          <t>1267447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1864609</t>
+          <t>1401038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>281298</t>
+          <t>46292</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36802</t>
+          <t>31559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>944600</t>
+          <t>66875</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>42992</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21135</t>
+          <t>30555</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>58714</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>313438</t>
+          <t>89284</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66409</t>
+          <t>70155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1089093</t>
+          <t>113321</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2234288</t>
+          <t>2167797</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2234288</t>
+          <t>2167797</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2234288</t>
+          <t>2167797</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4524615</t>
+          <t>4398363</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4524615</t>
+          <t>4398363</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4524615</t>
+          <t>4398363</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17900</t>
+          <t>17211</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>13638</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19302</t>
+          <t>23208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>21377</t>
+          <t>22771</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>15581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31531</t>
+          <t>33715</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>67931</t>
+          <t>75486</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54998</t>
+          <t>59405</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86668</t>
+          <t>94548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>96874</t>
+          <t>104897</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81752</t>
+          <t>89850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115173</t>
+          <t>123454</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>164805</t>
+          <t>180382</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143558</t>
+          <t>158652</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>188427</t>
+          <t>205780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>388430</t>
+          <t>424669</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>361092</t>
+          <t>391279</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>414973</t>
+          <t>451456</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>403266</t>
+          <t>439815</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>383863</t>
+          <t>414957</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>426273</t>
+          <t>462055</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>791696</t>
+          <t>864484</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>756947</t>
+          <t>826702</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>829089</t>
+          <t>899826</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>62,25%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>166652</t>
+          <t>186152</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>143152</t>
+          <t>160570</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>196619</t>
+          <t>214609</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>142447</t>
+          <t>167937</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>124314</t>
+          <t>148793</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159931</t>
+          <t>191750</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>309099</t>
+          <t>354089</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>277603</t>
+          <t>321736</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>344413</t>
+          <t>388447</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29400</t>
+          <t>30234</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10496</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>19234</t>
+          <t>23889</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10243</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32062</t>
+          <t>39482</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>659588</t>
+          <t>734028</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>659588</t>
+          <t>734028</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>659588</t>
+          <t>734028</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1306211</t>
+          <t>1445615</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1306211</t>
+          <t>1445615</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1306211</t>
+          <t>1445615</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>28097</t>
+          <t>33094</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18242</t>
+          <t>22688</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42219</t>
+          <t>49195</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>36710</t>
+          <t>43037</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27057</t>
+          <t>32157</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50255</t>
+          <t>57290</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>64807</t>
+          <t>76132</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50198</t>
+          <t>60476</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82209</t>
+          <t>95367</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>264567</t>
+          <t>287300</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>206982</t>
+          <t>254563</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>308784</t>
+          <t>326157</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>352168</t>
+          <t>381606</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>293078</t>
+          <t>350315</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>393061</t>
+          <t>418063</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>616735</t>
+          <t>668905</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>538182</t>
+          <t>622240</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>685361</t>
+          <t>726645</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1903604</t>
+          <t>2057590</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1464008</t>
+          <t>1995941</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2070663</t>
+          <t>2120935</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2012737</t>
+          <t>2158932</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1574504</t>
+          <t>2102437</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2170310</t>
+          <t>2211125</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3916341</t>
+          <t>4216522</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3364000</t>
+          <t>4121067</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4182705</t>
+          <t>4295581</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,3%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>944461</t>
+          <t>1062901</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>742901</t>
+          <t>1003282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1038461</t>
+          <t>1125385</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,22 +3145,22 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1193863</t>
+          <t>1070143</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1004934</t>
+          <t>1025566</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1727201</t>
+          <t>1125424</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2138324</t>
+          <t>2133044</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1894935</t>
+          <t>2054717</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2645256</t>
+          <t>2216536</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>311160</t>
+          <t>79798</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65659</t>
+          <t>62097</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>991975</t>
+          <t>104904</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>52840</t>
+          <t>69046</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>39377</t>
+          <t>53106</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69428</t>
+          <t>87353</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>364001</t>
+          <t>148844</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>114613</t>
+          <t>125782</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1189717</t>
+          <t>182342</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3648318</t>
+          <t>3722764</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3648318</t>
+          <t>3722764</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3648318</t>
+          <t>3722764</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7100207</t>
+          <t>7243447</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7100207</t>
+          <t>7243447</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7100207</t>
+          <t>7243447</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
